--- a/input_data/ccrvb15_olinkALVACALFQA_KCG_list_of_vars.xlsx
+++ b/input_data/ccrvb15_olinkALVACALFQA_KCG_list_of_vars.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="159">
   <si>
     <t xml:space="preserve">CCL8</t>
   </si>
@@ -157,43 +157,10 @@
     <t xml:space="preserve">MMP1</t>
   </si>
   <si>
-    <t xml:space="preserve">ELISA_IgG_ABL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IgG1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IgG2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IgG3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IgG4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ELISA_Lin_Biot_V2b_115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ELISA_Hel_Biot_V2c_150</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EISA_gp120ΔV1_ABL</t>
-  </si>
-  <si>
     <t xml:space="preserve">AvidityScore_SIV_M766_DV1_gp120</t>
   </si>
   <si>
-    <t xml:space="preserve">AvityScore_V2b115</t>
-  </si>
-  <si>
     <t xml:space="preserve">AvidityScore_V2c150</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AvityScore_SIVmac251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RectalELISASIVM766deltaV1gp120</t>
   </si>
   <si>
     <t xml:space="preserve">OD_V2_pep_25</t>
@@ -1139,61 +1106,6 @@
         <v>53</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="s">
-        <v>64</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -1207,27 +1119,27 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -1243,12 +1155,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -1264,47 +1176,47 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -1320,182 +1232,182 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>
@@ -1511,92 +1423,92 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>130</v>
+        <v>119</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
     </row>
   </sheetData>
@@ -1612,17 +1524,17 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
     </row>
   </sheetData>
@@ -1638,162 +1550,162 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>155</v>
+        <v>144</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>158</v>
+        <v>147</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>159</v>
+        <v>148</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>161</v>
+        <v>150</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>162</v>
+        <v>151</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>163</v>
+        <v>152</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
     </row>
   </sheetData>
